--- a/docs/capturas/flujos/SIGOV_reporte_diario_2026-08-31.xlsx
+++ b/docs/capturas/flujos/SIGOV_reporte_diario_2026-08-31.xlsx
@@ -65,7 +65,7 @@
     <t>FECHA DE EMISION</t>
   </si>
   <si>
-    <t>31/8/2026, 10:45:54 a. m.</t>
+    <t>31/8/2026, 6:11:56 p. m.</t>
   </si>
   <si>
     <t>HOJAS</t>
